--- a/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_CPU_SAO.xlsx
+++ b/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_CPU_SAO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manas/Documents/PyFock/benchmarks_tests/FINAL_Benchmarks_for_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3552A4D8-2567-8340-A645-A1438A467C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B761756E-F1C9-704A-8187-AC6943783E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="760" windowWidth="28040" windowHeight="16840" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
+    <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="16800" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
   </bookViews>
   <sheets>
     <sheet name="def2-SVP" sheetId="1" r:id="rId1"/>

--- a/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_CPU_SAO.xlsx
+++ b/benchmarks_tests/FINAL_Benchmarks_for_paper/PyFock_scaling_behavior_CPU_SAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manas/Documents/PyFock/benchmarks_tests/FINAL_Benchmarks_for_paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B761756E-F1C9-704A-8187-AC6943783E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F16576-F26C-1345-B9BA-8D9AF125D044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1360" yWindow="760" windowWidth="28040" windowHeight="16800" xr2:uid="{580CF0B2-FD39-1547-AD8E-82680C382266}"/>
   </bookViews>
